--- a/naver-place-crawler/results_health/세종_PT.xlsx
+++ b/naver-place-crawler/results_health/세종_PT.xlsx
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1046</v>
+        <v>1054</v>
       </c>
       <c r="Q2" t="n">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="R2" t="n">
-        <v>1373</v>
+        <v>1384</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="Q3" t="n">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="R3" t="n">
-        <v>580</v>
+        <v>616</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>플레토 피트니스 PT&amp;헬스\u002F파워리프팅</t>
+          <t>이루트핏PT 세종점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pleto_fit@naver.com</t>
+          <t>eroootfit@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1327-2196</t>
+          <t>0507-1335-1281</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>세종 세종로 1215 아성프라자 4층</t>
+          <t>세종 시청대로 213 베네치아 3층 E Root FIT</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pleto_strength_conditioning/</t>
+          <t>https://blog.naver.com/eroootfit</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcsanb</t>
+          <t>https://talk.naver.com/ct/w5z6v2</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>589</v>
+        <v>245</v>
       </c>
       <c r="Q4" t="n">
-        <v>460</v>
+        <v>120</v>
       </c>
       <c r="R4" t="n">
-        <v>1049</v>
+        <v>365</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1618611841</t>
+          <t>1338396603</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1618611841</t>
+          <t>https://m.place.naver.com/place/1338396603</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -858,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>이루트핏PT 세종점</t>
+          <t>퍼스트랩PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>eroootfit@naver.com</t>
+          <t>efuekbh1@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1335-1281</t>
+          <t>0507-1419-0844</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>세종 시청대로 213 베네치아 3층 E Root FIT</t>
+          <t>세종 나성북로 9 메가타워1 9층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/eroootfit</t>
+          <t>https://blog.naver.com/efuekbh1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5z6v2</t>
+          <t>https://talk.naver.com/ct/w4tt6n</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>211</v>
+        <v>254</v>
       </c>
       <c r="Q5" t="n">
-        <v>116</v>
+        <v>589</v>
       </c>
       <c r="R5" t="n">
-        <v>327</v>
+        <v>843</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +934,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1338396603</t>
+          <t>275402343</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1338396603</t>
+          <t>https://m.place.naver.com/place/275402343</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -956,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>나아짐 PT 운동센터</t>
+          <t>플레토 피트니스 PT&amp;헬스\u002F파워리프팅</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>naa_gym@naver.com</t>
+          <t>pleto_fit@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1480-1760</t>
+          <t>0507-1327-2196</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>세종 한누리대로 194 209호</t>
+          <t>세종 세종로 1215 아성프라자 4층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/naa_gymm</t>
+          <t>https://www.instagram.com/pleto_strength_conditioning/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wro1i1u</t>
+          <t>https://talk.naver.com/ct/wcsanb</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>590</v>
       </c>
       <c r="Q6" t="n">
-        <v>82</v>
+        <v>460</v>
       </c>
       <c r="R6" t="n">
-        <v>82</v>
+        <v>1050</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2098335357</t>
+          <t>1618611841</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2098335357</t>
+          <t>https://m.place.naver.com/place/1618611841</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1054,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>길라잡이체육관PT 세종본점</t>
+          <t>아워짐 PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sonhyangdeok@naver.com</t>
+          <t>tway7@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1324-1089</t>
+          <t>0507-1376-0254</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>세종 도움1로 108 5층 길라잡이 체육관</t>
+          <t>세종 호려울로 9 네이버타워 3층 아워짐 PT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sonhyangdeok</t>
+          <t>https://blog.naver.com/tway7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4otz4</t>
+          <t>https://talk.naver.com/ct/wfgh2xz</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1123</v>
+        <v>578</v>
       </c>
       <c r="Q7" t="n">
-        <v>235</v>
+        <v>317</v>
       </c>
       <c r="R7" t="n">
-        <v>1358</v>
+        <v>895</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1130,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1797638929</t>
+          <t>1143177695</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1797638929</t>
+          <t>https://m.place.naver.com/place/1143177695</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1152,29 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>퍼스트랩PT</t>
+          <t>길라잡이체육관PT 세종본점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>efuekbh1@naver.com</t>
+          <t>sonhyangdeok@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1419-0844</t>
+          <t>0507-1324-1089</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>세종 나성북로 9 메가타워1 9층</t>
+          <t>세종 도움1로 108 5층 길라잡이 체육관</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/efuekbh1</t>
+          <t>https://blog.naver.com/sonhyangdeok</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4tt6n</t>
+          <t>https://talk.naver.com/ct/w4otz4</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>252</v>
+        <v>1127</v>
       </c>
       <c r="Q8" t="n">
-        <v>581</v>
+        <v>237</v>
       </c>
       <c r="R8" t="n">
-        <v>833</v>
+        <v>1364</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>275402343</t>
+          <t>1797638929</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/275402343</t>
+          <t>https://m.place.naver.com/place/1797638929</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>아이브 피트니스 헬스 &amp; PT</t>
+          <t>온어스피트니스 헬스&amp;PT 세종종촌점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dlaeotn00@naver.com</t>
+          <t>onus_hyun@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1470-0860</t>
+          <t>0507-1440-2604</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>세종 시청대로 531 4층 전체</t>
+          <t>세종 도움1로 106 8층 806호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/fitness_iv</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wjsbr3a</t>
+          <t>https://talk.naver.com/ct/wy4z3k3</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,17 +1307,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>486</v>
+        <v>97</v>
       </c>
       <c r="Q9" t="n">
-        <v>123</v>
+        <v>326</v>
       </c>
       <c r="R9" t="n">
-        <v>609</v>
+        <v>423</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,17 +1326,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1878574714</t>
+          <t>2023654395</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1878574714</t>
+          <t>https://m.place.naver.com/place/2023654395</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1412,10 +1412,10 @@
         <v>604</v>
       </c>
       <c r="Q10" t="n">
-        <v>2402</v>
+        <v>2405</v>
       </c>
       <c r="R10" t="n">
-        <v>3006</v>
+        <v>3009</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1434,41 +1434,41 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>온어스필라테스&amp;PT 세종새롬점</t>
+          <t>마음바른휘트니스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>rabit123_@naver.com</t>
+          <t>maumbarnfit@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1492-2508</t>
+          <t>0507-1390-0466</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>세종 새롬중앙로 67 202호</t>
+          <t>세종 보듬3로 160 아이콤타워 5F</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/maumbarnfit</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1493,27 +1493,27 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wb7xp56</t>
+          <t>https://talk.naver.com/ct/w4sy7b</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>84</v>
+        <v>157</v>
       </c>
       <c r="Q11" t="n">
-        <v>942</v>
+        <v>477</v>
       </c>
       <c r="R11" t="n">
-        <v>1026</v>
+        <v>634</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,47 +1522,51 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1993969527</t>
+          <t>1767406668</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1993969527</t>
+          <t>https://m.place.naver.com/place/1767406668</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>달라짐 PT</t>
+          <t>온어스필라테스&amp;PT 세종새롬점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ddoddo780@naver.com</t>
+          <t>mbh_00@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1492-2508</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>세종 한누리대로 2257 2층 202호 달라짐</t>
+          <t>세종 새롬중앙로 67 202호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dallagym_pt?igsh=eGk5dGV3dGsxdmMw</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1572,7 +1576,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1587,27 +1591,27 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wihac2x</t>
+          <t>https://talk.naver.com/ct/wb7xp56</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="Q12" t="n">
-        <v>42</v>
+        <v>951</v>
       </c>
       <c r="R12" t="n">
-        <v>88</v>
+        <v>1037</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1616,17 +1620,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1260151471</t>
+          <t>1993969527</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1260151471</t>
+          <t>https://m.place.naver.com/place/1993969527</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/세종_PT.xlsx
+++ b/naver-place-crawler/results_health/세종_PT.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1054</v>
+        <v>1059</v>
       </c>
       <c r="Q2" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="R2" t="n">
-        <v>1384</v>
+        <v>1390</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="Q3" t="n">
         <v>523</v>
       </c>
       <c r="R3" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>이루트핏PT 세종점</t>
+          <t>길라잡이체육관PT 어진점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>eroootfit@naver.com</t>
+          <t>sonhyangdeok1@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1335-1281</t>
+          <t>0507-1470-7831</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>세종 시청대로 213 베네치아 3층 E Root FIT</t>
+          <t>세종 절재로 194 중앙타운 803호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/eroootfit</t>
+          <t>https://blog.naver.com/sonhyangdeok1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5z6v2</t>
+          <t>https://talk.naver.com/ct/wbql9cd</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>245</v>
+        <v>552</v>
       </c>
       <c r="Q4" t="n">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="R4" t="n">
-        <v>365</v>
+        <v>666</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1338396603</t>
+          <t>1143360999</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1338396603</t>
+          <t>https://m.place.naver.com/place/1143360999</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -922,10 +922,10 @@
         <v>254</v>
       </c>
       <c r="Q5" t="n">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="R5" t="n">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -956,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>플레토 피트니스 PT&amp;헬스\u002F파워리프팅</t>
+          <t>이루트핏PT 세종점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pleto_fit@naver.com</t>
+          <t>eroootfit@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1327-2196</t>
+          <t>0507-1335-1281</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>세종 세종로 1215 아성프라자 4층</t>
+          <t>세종 시청대로 213 베네치아 3층 E Root FIT</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pleto_strength_conditioning/</t>
+          <t>https://blog.naver.com/eroootfit</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcsanb</t>
+          <t>https://talk.naver.com/ct/w5z6v2</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>590</v>
+        <v>247</v>
       </c>
       <c r="Q6" t="n">
-        <v>460</v>
+        <v>120</v>
       </c>
       <c r="R6" t="n">
-        <v>1050</v>
+        <v>367</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1618611841</t>
+          <t>1338396603</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1618611841</t>
+          <t>https://m.place.naver.com/place/1338396603</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1054,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>아워짐 PT</t>
+          <t>플레토 피트니스 PT&amp;헬스\u002F파워리프팅</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>tway7@naver.com</t>
+          <t>pleto_fit@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1376-0254</t>
+          <t>0507-1327-2196</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>세종 호려울로 9 네이버타워 3층 아워짐 PT</t>
+          <t>세종 세종로 1215 아성프라자 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tway7</t>
+          <t>https://www.instagram.com/pleto_strength_conditioning/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wfgh2xz</t>
+          <t>https://talk.naver.com/ct/wcsanb</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="Q7" t="n">
-        <v>317</v>
+        <v>460</v>
       </c>
       <c r="R7" t="n">
-        <v>895</v>
+        <v>1050</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1130,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1143177695</t>
+          <t>1618611841</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1143177695</t>
+          <t>https://m.place.naver.com/place/1618611841</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1152,29 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>길라잡이체육관PT 세종본점</t>
+          <t>아워짐 PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sonhyangdeok@naver.com</t>
+          <t>tway7@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1324-1089</t>
+          <t>0507-1376-0254</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>세종 도움1로 108 5층 길라잡이 체육관</t>
+          <t>세종 호려울로 9 네이버타워 3층 아워짐 PT</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sonhyangdeok</t>
+          <t>https://blog.naver.com/tway7</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4otz4</t>
+          <t>https://talk.naver.com/ct/wfgh2xz</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1127</v>
+        <v>578</v>
       </c>
       <c r="Q8" t="n">
-        <v>237</v>
+        <v>318</v>
       </c>
       <c r="R8" t="n">
-        <v>1364</v>
+        <v>896</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1797638929</t>
+          <t>1143177695</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1797638929</t>
+          <t>https://m.place.naver.com/place/1143177695</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q9" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="R9" t="n">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1336,41 +1336,41 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>온어스필라테스 재활운동 세종아름점</t>
+          <t>나인원핏 헬스&amp;PT 세종나성점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>kcyd48@naver.com</t>
+          <t>2riwabang@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1350-1047</t>
+          <t>0507-1352-8382</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>세종 보듬3로 91 해피라움4 2층 201호</t>
+          <t>세종 한누리대로 316 세종마루2 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/2riwabang/224083548666</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4bjvz</t>
+          <t>https://talk.naver.com/ct/w4cwph</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,17 +1405,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>604</v>
+        <v>706</v>
       </c>
       <c r="Q10" t="n">
-        <v>2405</v>
+        <v>882</v>
       </c>
       <c r="R10" t="n">
-        <v>3009</v>
+        <v>1588</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,51 +1424,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1758028876</t>
+          <t>1575294603</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1758028876</t>
+          <t>https://m.place.naver.com/place/1575294603</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>마음바른휘트니스</t>
+          <t>온어스필라테스 재활운동 세종아름점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>maumbarnfit@naver.com</t>
+          <t>kcyd48@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1390-0466</t>
+          <t>0507-1350-1047</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>세종 보듬3로 160 아이콤타워 5F</t>
+          <t>세종 보듬3로 91 해피라움4 2층 201호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/maumbarnfit</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1493,27 +1493,27 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4sy7b</t>
+          <t>https://talk.naver.com/ct/w4bjvz</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>157</v>
+        <v>605</v>
       </c>
       <c r="Q11" t="n">
-        <v>477</v>
+        <v>2411</v>
       </c>
       <c r="R11" t="n">
-        <v>634</v>
+        <v>3016</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,115 +1522,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1767406668</t>
+          <t>1758028876</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1767406668</t>
+          <t>https://m.place.naver.com/place/1758028876</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>필라테스</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>온어스필라테스&amp;PT 세종새롬점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>mbh_00@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1492-2508</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>세종 새롬중앙로 67 202호</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wb7xp56</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>86</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>951</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1037</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1993969527</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1993969527</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/세종_PT.xlsx
+++ b/naver-place-crawler/results_health/세종_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1409,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="Q10" t="n">
         <v>882</v>
       </c>
       <c r="R10" t="n">
-        <v>1588</v>
+        <v>1593</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         <v>605</v>
       </c>
       <c r="Q11" t="n">
-        <v>2411</v>
+        <v>2412</v>
       </c>
       <c r="R11" t="n">
-        <v>3016</v>
+        <v>3017</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1531,6 +1531,104 @@
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>마음바른휘트니스</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>maumbarnfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1390-0466</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>세종 보듬3로 160 아이콤타워 5F</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maumbarnfit</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4sy7b</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>157</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>477</v>
+      </c>
+      <c r="R12" t="n">
+        <v>634</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1767406668</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1767406668</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/세종_PT.xlsx
+++ b/naver-place-crawler/results_health/세종_PT.xlsx
@@ -628,10 +628,10 @@
         <v>1059</v>
       </c>
       <c r="Q2" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="R2" t="n">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q3" t="n">
         <v>523</v>
       </c>
       <c r="R3" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>세종 절재로 194 중앙타운 803호</t>
+          <t>세종 절재로 194 ��앙타운 803호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1343,34 +1343,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>나인원핏 헬스&amp;PT 세종나성점</t>
+          <t>온어스필라테스 재활운동 세종아름점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2riwabang@naver.com</t>
+          <t>kcyd48@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1352-8382</t>
+          <t>0507-1350-1047</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>세종 한누리대로 316 세종마루2 2층</t>
+          <t>세종 보듬3로 91 해피라움4 2층 201호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/2riwabang/224083548666</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4cwph</t>
+          <t>https://talk.naver.com/ct/w4bjvz</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,17 +1405,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>711</v>
+        <v>605</v>
       </c>
       <c r="Q10" t="n">
-        <v>882</v>
+        <v>2412</v>
       </c>
       <c r="R10" t="n">
-        <v>1593</v>
+        <v>3017</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1575294603</t>
+          <t>1758028876</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1575294603</t>
+          <t>https://m.place.naver.com/place/1758028876</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1441,34 +1441,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>온어스필라테스 재활운동 세종아름점</t>
+          <t>마음바른휘트니스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>kcyd48@naver.com</t>
+          <t>maumbarnfit@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1350-1047</t>
+          <t>0507-1390-0466</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>세종 보듬3로 91 해피라움4 2층 201호</t>
+          <t>세종 보듬3로 160 아이콤타워 5F</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/maumbarnfit</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1493,27 +1493,27 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4bjvz</t>
+          <t>https://talk.naver.com/ct/w4sy7b</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>605</v>
+        <v>157</v>
       </c>
       <c r="Q11" t="n">
-        <v>2412</v>
+        <v>477</v>
       </c>
       <c r="R11" t="n">
-        <v>3017</v>
+        <v>634</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1758028876</t>
+          <t>1767406668</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1758028876</t>
+          <t>https://m.place.naver.com/place/1767406668</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1539,34 +1539,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>마음바른휘트니스</t>
+          <t>온어스필라테스&amp;PT 세종새롬점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>maumbarnfit@naver.com</t>
+          <t>mbh_00@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1390-0466</t>
+          <t>0507-1492-2508</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>세종 보듬3로 160 아이콤타워 5F</t>
+          <t>세종 새롬중앙로 67 202호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/maumbarnfit</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1591,27 +1591,27 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4sy7b</t>
+          <t>https://talk.naver.com/ct/wb7xp56</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>157</v>
+        <v>86</v>
       </c>
       <c r="Q12" t="n">
-        <v>477</v>
+        <v>959</v>
       </c>
       <c r="R12" t="n">
-        <v>634</v>
+        <v>1045</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1620,12 +1620,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1767406668</t>
+          <t>1993969527</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1767406668</t>
+          <t>https://m.place.naver.com/place/1993969527</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">

--- a/naver-place-crawler/results_health/세종_PT.xlsx
+++ b/naver-place-crawler/results_health/세종_PT.xlsx
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="Q2" t="n">
         <v>332</v>
       </c>
       <c r="R2" t="n">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q3" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="R3" t="n">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>세종 절재로 194 ��앙타운 803호</t>
+          <t>세종 절재로 194 중앙타운 803호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="Q4" t="n">
         <v>114</v>
       </c>
       <c r="R4" t="n">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q6" t="n">
         <v>120</v>
       </c>
       <c r="R6" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1245,29 +1245,29 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>온어스피트니스 헬스&amp;PT 세종종촌점</t>
+          <t>온어스필라테스 재활운동 세종아름점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>onus_hyun@naver.com</t>
+          <t>kcyd48@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1440-2604</t>
+          <t>0507-1350-1047</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>세종 도움1로 106 8층 806호</t>
+          <t>세종 보듬3로 91 해피라움4 2층 201호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wy4z3k3</t>
+          <t>https://talk.naver.com/ct/w4bjvz</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>98</v>
+        <v>605</v>
       </c>
       <c r="Q9" t="n">
-        <v>328</v>
+        <v>2415</v>
       </c>
       <c r="R9" t="n">
-        <v>426</v>
+        <v>3020</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2023654395</t>
+          <t>1758028876</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2023654395</t>
+          <t>https://m.place.naver.com/place/1758028876</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1343,34 +1343,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>온어스필라테스 재활운동 세종아름점</t>
+          <t>마음바른휘트니스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>kcyd48@naver.com</t>
+          <t>maumbarnfit@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1350-1047</t>
+          <t>0507-1390-0466</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>세종 보듬3로 91 해피라움4 2층 201호</t>
+          <t>세종 보듬3로 160 아이콤타워 5F</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/maumbarnfit</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1395,27 +1395,27 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4bjvz</t>
+          <t>https://talk.naver.com/ct/w4sy7b</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>605</v>
+        <v>157</v>
       </c>
       <c r="Q10" t="n">
-        <v>2412</v>
+        <v>477</v>
       </c>
       <c r="R10" t="n">
-        <v>3017</v>
+        <v>634</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1758028876</t>
+          <t>1767406668</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1758028876</t>
+          <t>https://m.place.naver.com/place/1767406668</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1441,34 +1441,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>마음바른휘트니스</t>
+          <t>온어스필라테스&amp;PT 세종새롬점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>maumbarnfit@naver.com</t>
+          <t>mbh_00@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1390-0466</t>
+          <t>0507-1492-2508</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>세종 보듬3로 160 아이콤타워 5F</t>
+          <t>세종 새롬중앙로 67 202호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/maumbarnfit</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1493,27 +1493,27 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4sy7b</t>
+          <t>https://talk.naver.com/ct/wb7xp56</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>157</v>
+        <v>86</v>
       </c>
       <c r="Q11" t="n">
-        <v>477</v>
+        <v>960</v>
       </c>
       <c r="R11" t="n">
-        <v>634</v>
+        <v>1046</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1767406668</t>
+          <t>1993969527</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1767406668</t>
+          <t>https://m.place.naver.com/place/1993969527</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1539,34 +1539,30 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>온어스필라테스&amp;PT 세종새롬점</t>
+          <t>달라짐 PT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>mbh_00@naver.com</t>
+          <t>ddoddo780@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1492-2508</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>세종 새롬중앙로 67 202호</t>
+          <t>세종 한누리대로 2257 2층 202호 달라짐</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/dallagym_pt?igsh=eGk5dGV3dGsxdmMw</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1576,7 +1572,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1591,27 +1587,27 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wb7xp56</t>
+          <t>https://talk.naver.com/ct/wihac2x</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="Q12" t="n">
-        <v>959</v>
+        <v>43</v>
       </c>
       <c r="R12" t="n">
-        <v>1045</v>
+        <v>90</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1620,12 +1616,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1993969527</t>
+          <t>1260151471</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1993969527</t>
+          <t>https://m.place.naver.com/place/1260151471</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">

--- a/naver-place-crawler/results_health/세종_PT.xlsx
+++ b/naver-place-crawler/results_health/세종_PT.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1238,36 +1238,36 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>온어스필라테스 재활운동 세종아름점</t>
+          <t>온어스피트니스 헬스&amp;PT 세종종촌점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kcyd48@naver.com</t>
+          <t>onus_hyun@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1350-1047</t>
+          <t>0507-1440-2604</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>세종 보듬3로 91 해피라움4 2층 201호</t>
+          <t>세종 도움1로 106 8층 806호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4bjvz</t>
+          <t>https://talk.naver.com/ct/wy4z3k3</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>605</v>
+        <v>98</v>
       </c>
       <c r="Q9" t="n">
-        <v>2415</v>
+        <v>328</v>
       </c>
       <c r="R9" t="n">
-        <v>3020</v>
+        <v>426</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,17 +1326,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1758028876</t>
+          <t>2023654395</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1758028876</t>
+          <t>https://m.place.naver.com/place/2023654395</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1348,29 +1348,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>마음바른휘트니스</t>
+          <t>나인원핏 헬스&amp;PT 세종나성점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>maumbarnfit@naver.com</t>
+          <t>2riwabang@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1390-0466</t>
+          <t>0507-1352-8382</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>세종 보듬3로 160 아이콤타워 5F</t>
+          <t>세종 한누리대로 316 세종마루2 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/maumbarnfit</t>
+          <t>https://blog.naver.com/2riwabang/224083548666</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1395,12 +1395,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4sy7b</t>
+          <t>https://talk.naver.com/ct/w4cwph</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1409,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>157</v>
+        <v>719</v>
       </c>
       <c r="Q10" t="n">
-        <v>477</v>
+        <v>882</v>
       </c>
       <c r="R10" t="n">
-        <v>634</v>
+        <v>1601</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,17 +1424,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1767406668</t>
+          <t>1575294603</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1767406668</t>
+          <t>https://m.place.naver.com/place/1575294603</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1446,24 +1446,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>온어스필라테스&amp;PT 세종새롬점</t>
+          <t>온어스필라테스 재활운동 세종아름점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mbh_00@naver.com</t>
+          <t>kcyd48@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1492-2508</t>
+          <t>0507-1350-1047</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>세종 새롬중앙로 67 202호</t>
+          <t>세종 보듬3로 91 해피라움4 2층 201호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wb7xp56</t>
+          <t>https://talk.naver.com/ct/w4bjvz</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>86</v>
+        <v>605</v>
       </c>
       <c r="Q11" t="n">
-        <v>960</v>
+        <v>2415</v>
       </c>
       <c r="R11" t="n">
-        <v>1046</v>
+        <v>3020</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,47 +1522,51 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1993969527</t>
+          <t>1758028876</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1993969527</t>
+          <t>https://m.place.naver.com/place/1758028876</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>달라짐 PT</t>
+          <t>마음바른휘트니스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ddoddo780@naver.com</t>
+          <t>maumbarnfit@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1390-0466</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>세종 한누리대로 2257 2층 202호 달라짐</t>
+          <t>세종 보듬3로 160 아이콤타워 5F</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dallagym_pt?igsh=eGk5dGV3dGsxdmMw</t>
+          <t>https://www.instagram.com/maumbarnfit</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1587,7 +1591,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wihac2x</t>
+          <t>https://talk.naver.com/ct/w4sy7b</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1601,13 +1605,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>47</v>
+        <v>157</v>
       </c>
       <c r="Q12" t="n">
-        <v>43</v>
+        <v>477</v>
       </c>
       <c r="R12" t="n">
-        <v>90</v>
+        <v>634</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1616,17 +1620,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1260151471</t>
+          <t>1767406668</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1260151471</t>
+          <t>https://m.place.naver.com/place/1767406668</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/세종_PT.xlsx
+++ b/naver-place-crawler/results_health/세종_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="Q3" t="n">
         <v>524</v>
       </c>
       <c r="R3" t="n">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q5" t="n">
         <v>120</v>
       </c>
       <c r="R5" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1348,29 +1348,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>마음바른휘트니스</t>
+          <t>온어스피트니스 헬스&amp;PT 세종종촌점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>maumbarnfit@naver.com</t>
+          <t>onus_hyun@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1390-0466</t>
+          <t>0507-1440-2604</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>세종 보듬3로 160 아이콤타워 5F</t>
+          <t>세종 도움1로 106 8층 806호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/maumbarnfit</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1395,27 +1395,27 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4sy7b</t>
+          <t>https://talk.naver.com/ct/wy4z3k3</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>157</v>
+        <v>99</v>
       </c>
       <c r="Q10" t="n">
-        <v>477</v>
+        <v>329</v>
       </c>
       <c r="R10" t="n">
-        <v>634</v>
+        <v>428</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,51 +1424,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1767406668</t>
+          <t>2023654395</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1767406668</t>
+          <t>https://m.place.naver.com/place/2023654395</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>온어스필라테스 재활운동 세종아름점</t>
+          <t>나인원핏 헬스&amp;PT 세종나성점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>kcyd48@naver.com</t>
+          <t>2riwabang@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1350-1047</t>
+          <t>0507-1352-8382</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>세종 보듬3로 91 해피라움4 2층 201호</t>
+          <t>세종 한누리대로 316 세종마루2 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/2riwabang/224083548666</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4bjvz</t>
+          <t>https://talk.naver.com/ct/w4cwph</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1503,17 +1503,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>605</v>
+        <v>720</v>
       </c>
       <c r="Q11" t="n">
-        <v>2420</v>
+        <v>882</v>
       </c>
       <c r="R11" t="n">
-        <v>3025</v>
+        <v>1602</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,51 +1522,51 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1758028876</t>
+          <t>1575294603</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1758028876</t>
+          <t>https://m.place.naver.com/place/1575294603</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>온어스필라테스&amp;PT 세종새롬점</t>
+          <t>마음바른휘트니스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>yunnovel@naver.com</t>
+          <t>maumbarnfit@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1492-2508</t>
+          <t>0507-1390-0466</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>세종 새롬중앙로 67 202호</t>
+          <t>세종 보듬3로 160 아이콤타워 5F</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/maumbarnfit</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1591,27 +1591,27 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wb7xp56</t>
+          <t>https://talk.naver.com/ct/w4sy7b</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>86</v>
+        <v>157</v>
       </c>
       <c r="Q12" t="n">
-        <v>965</v>
+        <v>477</v>
       </c>
       <c r="R12" t="n">
-        <v>1051</v>
+        <v>634</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1620,17 +1620,115 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1993969527</t>
+          <t>1767406668</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1993969527</t>
+          <t>https://m.place.naver.com/place/1767406668</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>온어스필라테스 재활운동 세종아름점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>kcyd48@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1350-1047</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>세종 보듬3로 91 해피라움4 2층 201호</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4bjvz</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>605</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2421</v>
+      </c>
+      <c r="R13" t="n">
+        <v>3026</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1758028876</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1758028876</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/세종_PT.xlsx
+++ b/naver-place-crawler/results_health/세종_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -726,10 +726,10 @@
         <v>101</v>
       </c>
       <c r="Q3" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="R3" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -858,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>이루트핏PT 세종점</t>
+          <t>플레토 피트니스 PT&amp;헬스\u002F파워리프팅</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>eroootfit@naver.com</t>
+          <t>pleto_fit@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1335-1281</t>
+          <t>0507-1327-2196</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>세종 시청대로 213 베네치아 3층 E Root FIT</t>
+          <t>세종 세종로 1215 아성프라자 4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/eroootfit</t>
+          <t>https://www.instagram.com/pleto_strength_conditioning/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5z6v2</t>
+          <t>https://talk.naver.com/ct/wcsanb</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>254</v>
+        <v>590</v>
       </c>
       <c r="Q5" t="n">
-        <v>120</v>
+        <v>460</v>
       </c>
       <c r="R5" t="n">
-        <v>374</v>
+        <v>1050</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1338396603</t>
+          <t>1618611841</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1338396603</t>
+          <t>https://m.place.naver.com/place/1618611841</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -956,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>퍼스트랩PT</t>
+          <t>이루트핏PT 세종점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>efuekbh1@naver.com</t>
+          <t>eroootfit@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1419-0844</t>
+          <t>0507-1335-1281</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>세종 나성북로 9 메가타워1 9층</t>
+          <t>세종 시청대로 213 베네치아 3층 E Root FIT</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/efuekbh1</t>
+          <t>https://blog.naver.com/eroootfit</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4tt6n</t>
+          <t>https://talk.naver.com/ct/w5z6v2</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q6" t="n">
-        <v>590</v>
+        <v>120</v>
       </c>
       <c r="R6" t="n">
-        <v>844</v>
+        <v>377</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>275402343</t>
+          <t>1338396603</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/275402343</t>
+          <t>https://m.place.naver.com/place/1338396603</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1054,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>플레토 피트니스 PT&amp;헬스\u002F파워리프팅</t>
+          <t>퍼스트랩PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pleto_fit@naver.com</t>
+          <t>efuekbh1@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1327-2196</t>
+          <t>0507-1419-0844</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>세종 세종로 1215 아성프라자 4층</t>
+          <t>세종 나성북로 9 메가타워1 9층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pleto_strength_conditioning/</t>
+          <t>https://blog.naver.com/efuekbh1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcsanb</t>
+          <t>https://talk.naver.com/ct/w4tt6n</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
+        <v>254</v>
+      </c>
+      <c r="Q7" t="n">
         <v>590</v>
       </c>
-      <c r="Q7" t="n">
-        <v>460</v>
-      </c>
       <c r="R7" t="n">
-        <v>1050</v>
+        <v>844</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1618611841</t>
+          <t>275402343</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1618611841</t>
+          <t>https://m.place.naver.com/place/275402343</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1216,10 +1216,10 @@
         <v>578</v>
       </c>
       <c r="Q8" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="R8" t="n">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Q9" t="n">
         <v>130</v>
       </c>
       <c r="R9" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1412,10 +1412,10 @@
         <v>99</v>
       </c>
       <c r="Q10" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="R10" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>720</v>
+        <v>731</v>
       </c>
       <c r="Q11" t="n">
         <v>882</v>
       </c>
       <c r="R11" t="n">
-        <v>1602</v>
+        <v>1613</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1539,34 +1539,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>마음바른휘트니스</t>
+          <t>온어스필라테스 재활운동 세종아름점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>maumbarnfit@naver.com</t>
+          <t>kcyd48@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1390-0466</t>
+          <t>0507-1350-1047</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>세종 보듬3로 160 아이콤타워 5F</t>
+          <t>세종 보듬3로 91 해피라움4 2층 201호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/maumbarnfit</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1591,27 +1591,27 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4sy7b</t>
+          <t>https://talk.naver.com/ct/w4bjvz</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>157</v>
+        <v>605</v>
       </c>
       <c r="Q12" t="n">
-        <v>477</v>
+        <v>2421</v>
       </c>
       <c r="R12" t="n">
-        <v>634</v>
+        <v>3026</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1620,113 +1620,15 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1767406668</t>
+          <t>1758028876</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1767406668</t>
+          <t>https://m.place.naver.com/place/1758028876</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>필라테스</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>온어스필라테스 재활운동 세종아름점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>kcyd48@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1350-1047</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>세종 보듬3로 91 해피라움4 2층 201호</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4bjvz</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>605</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2421</v>
-      </c>
-      <c r="R13" t="n">
-        <v>3026</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1758028876</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1758028876</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>

--- a/naver-place-crawler/results_health/세종_PT.xlsx
+++ b/naver-place-crawler/results_health/세종_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="Q2" t="n">
         <v>332</v>
       </c>
       <c r="R2" t="n">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -726,10 +726,10 @@
         <v>101</v>
       </c>
       <c r="Q3" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="R3" t="n">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q6" t="n">
         <v>120</v>
       </c>
       <c r="R6" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="Q9" t="n">
         <v>130</v>
       </c>
       <c r="R9" t="n">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="Q11" t="n">
         <v>882</v>
       </c>
       <c r="R11" t="n">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1532,105 +1532,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>필라테스</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>온어스필라테스 재활운동 세종아름점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>kcyd48@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1350-1047</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>세종 보듬3로 91 해피라움4 2층 201호</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4bjvz</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>605</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2421</v>
-      </c>
-      <c r="R12" t="n">
-        <v>3026</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1758028876</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1758028876</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/세종_PT.xlsx
+++ b/naver-place-crawler/results_health/세종_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="Q11" t="n">
         <v>882</v>
       </c>
       <c r="R11" t="n">
-        <v>1615</v>
+        <v>1618</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1531,6 +1531,104 @@
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>마음바른휘트니스</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>maumbarnfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1390-0466</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>세종 보듬3로 160 아이콤타워 5F</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maumbarnfit</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4sy7b</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>157</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>477</v>
+      </c>
+      <c r="R12" t="n">
+        <v>634</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1767406668</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1767406668</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
